--- a/app/templates_excel/albedo/a8_en.xlsx
+++ b/app/templates_excel/albedo/a8_en.xlsx
@@ -1184,10 +1184,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1444,10 +1440,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1572,10 +1564,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2336,10 +2324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2440,10 +2424,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2677,6 +2657,26 @@
   </si>
   <si>
     <t>A professor peering over his glasses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -17466,7 +17466,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -17493,93 +17493,93 @@
     </row>
     <row r="5" spans="1:23" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:23" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>701</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>702</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>704</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>705</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="H10" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="I10" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="J10" s="7" t="s">
         <v>708</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="K10" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="L10" s="7" t="s">
         <v>710</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>711</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="N10" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="O10" s="7" t="s">
         <v>713</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="P10" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="Q10" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="R10" s="7" t="s">
         <v>716</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="S10" s="7" t="s">
         <v>717</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="T10" s="7" t="s">
         <v>718</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="U10" s="7" t="s">
         <v>719</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>720</v>
-      </c>
-      <c r="R10" s="7" t="s">
-        <v>721</v>
-      </c>
-      <c r="S10" s="7" t="s">
-        <v>722</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>723</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>724</v>
-      </c>
       <c r="V10" s="7" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="W10" s="7" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="V11" s="9" t="s">
         <v>344</v>
@@ -17587,7 +17587,7 @@
     </row>
     <row r="12" spans="1:23" ht="15" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="V12" s="9" t="s">
         <v>345</v>
@@ -17819,75 +17819,75 @@
     </row>
     <row r="41" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V41" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W41" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A42" s="11" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="V42" s="9" t="s">
         <v>374</v>
@@ -17895,7 +17895,7 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A43" s="11" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="V43" s="9" t="s">
         <v>375</v>
@@ -17922,7 +17922,7 @@
         <v>30</v>
       </c>
       <c r="V46" s="9" t="s">
-        <v>378</v>
+        <v>748</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.4">
@@ -17930,7 +17930,7 @@
         <v>31</v>
       </c>
       <c r="V47" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.4">
@@ -17938,7 +17938,7 @@
         <v>32</v>
       </c>
       <c r="V48" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.4">
@@ -17946,7 +17946,7 @@
         <v>33</v>
       </c>
       <c r="V49" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.4">
@@ -17954,7 +17954,7 @@
         <v>34</v>
       </c>
       <c r="V50" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.4">
@@ -17962,7 +17962,7 @@
         <v>35</v>
       </c>
       <c r="V51" s="9" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.4">
@@ -17970,7 +17970,7 @@
         <v>36</v>
       </c>
       <c r="V52" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.4">
@@ -17978,7 +17978,7 @@
         <v>37</v>
       </c>
       <c r="V53" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.4">
@@ -17986,7 +17986,7 @@
         <v>38</v>
       </c>
       <c r="V54" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.4">
@@ -17994,7 +17994,7 @@
         <v>39</v>
       </c>
       <c r="V55" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.4">
@@ -18002,7 +18002,7 @@
         <v>40</v>
       </c>
       <c r="V56" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.4">
@@ -18010,7 +18010,7 @@
         <v>41</v>
       </c>
       <c r="V57" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.4">
@@ -18018,7 +18018,7 @@
         <v>42</v>
       </c>
       <c r="V58" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.4">
@@ -18026,7 +18026,7 @@
         <v>43</v>
       </c>
       <c r="V59" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.4">
@@ -18034,7 +18034,7 @@
         <v>44</v>
       </c>
       <c r="V60" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.4">
@@ -18042,7 +18042,7 @@
         <v>45</v>
       </c>
       <c r="V61" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.4">
@@ -18050,7 +18050,7 @@
         <v>46</v>
       </c>
       <c r="V62" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.4">
@@ -18058,7 +18058,7 @@
         <v>47</v>
       </c>
       <c r="V63" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.4">
@@ -18066,7 +18066,7 @@
         <v>48</v>
       </c>
       <c r="V64" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.4">
@@ -18074,7 +18074,7 @@
         <v>49</v>
       </c>
       <c r="V65" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.4">
@@ -18082,7 +18082,7 @@
         <v>50</v>
       </c>
       <c r="V66" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.4">
@@ -18090,7 +18090,7 @@
         <v>51</v>
       </c>
       <c r="V67" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.4">
@@ -18098,7 +18098,7 @@
         <v>52</v>
       </c>
       <c r="V68" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.4">
@@ -18106,7 +18106,7 @@
         <v>53</v>
       </c>
       <c r="V69" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.4">
@@ -18114,7 +18114,7 @@
         <v>54</v>
       </c>
       <c r="V70" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.4">
@@ -18122,91 +18122,91 @@
         <v>55</v>
       </c>
       <c r="V71" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="72" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V72" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W72" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A73" s="12" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="V73" s="9" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A74" s="12" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="V74" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.4">
@@ -18214,7 +18214,7 @@
         <v>56</v>
       </c>
       <c r="V75" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.4">
@@ -18222,7 +18222,7 @@
         <v>57</v>
       </c>
       <c r="V76" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.4">
@@ -18230,7 +18230,7 @@
         <v>58</v>
       </c>
       <c r="V77" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.4">
@@ -18238,7 +18238,7 @@
         <v>59</v>
       </c>
       <c r="V78" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.4">
@@ -18246,7 +18246,7 @@
         <v>60</v>
       </c>
       <c r="V79" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.4">
@@ -18254,7 +18254,7 @@
         <v>61</v>
       </c>
       <c r="V80" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.4">
@@ -18262,7 +18262,7 @@
         <v>62</v>
       </c>
       <c r="V81" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.4">
@@ -18270,7 +18270,7 @@
         <v>63</v>
       </c>
       <c r="V82" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.4">
@@ -18278,7 +18278,7 @@
         <v>64</v>
       </c>
       <c r="V83" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.4">
@@ -18286,7 +18286,7 @@
         <v>65</v>
       </c>
       <c r="V84" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.4">
@@ -18294,7 +18294,7 @@
         <v>66</v>
       </c>
       <c r="V85" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.4">
@@ -18302,7 +18302,7 @@
         <v>67</v>
       </c>
       <c r="V86" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.4">
@@ -18310,7 +18310,7 @@
         <v>68</v>
       </c>
       <c r="V87" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.4">
@@ -18318,7 +18318,7 @@
         <v>69</v>
       </c>
       <c r="V88" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.4">
@@ -18326,7 +18326,7 @@
         <v>70</v>
       </c>
       <c r="V89" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.4">
@@ -18334,7 +18334,7 @@
         <v>71</v>
       </c>
       <c r="V90" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.4">
@@ -18342,7 +18342,7 @@
         <v>72</v>
       </c>
       <c r="V91" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.4">
@@ -18350,7 +18350,7 @@
         <v>73</v>
       </c>
       <c r="V92" s="9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.4">
@@ -18358,7 +18358,7 @@
         <v>74</v>
       </c>
       <c r="V93" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.4">
@@ -18366,7 +18366,7 @@
         <v>75</v>
       </c>
       <c r="V94" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="95" spans="1:22" x14ac:dyDescent="0.4">
@@ -18374,7 +18374,7 @@
         <v>76</v>
       </c>
       <c r="V95" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="96" spans="1:22" x14ac:dyDescent="0.4">
@@ -18382,7 +18382,7 @@
         <v>77</v>
       </c>
       <c r="V96" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.4">
@@ -18390,7 +18390,7 @@
         <v>78</v>
       </c>
       <c r="V97" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.4">
@@ -18398,7 +18398,7 @@
         <v>79</v>
       </c>
       <c r="V98" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.4">
@@ -18406,7 +18406,7 @@
         <v>80</v>
       </c>
       <c r="V99" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.4">
@@ -18414,7 +18414,7 @@
         <v>81</v>
       </c>
       <c r="V100" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.4">
@@ -18422,7 +18422,7 @@
         <v>82</v>
       </c>
       <c r="V101" s="9" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.4">
@@ -18430,83 +18430,83 @@
         <v>83</v>
       </c>
       <c r="V102" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="103" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U103" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V103" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W103" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A104" s="13" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="V104" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.4">
@@ -18514,7 +18514,7 @@
         <v>84</v>
       </c>
       <c r="V105" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.4">
@@ -18522,7 +18522,7 @@
         <v>85</v>
       </c>
       <c r="V106" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.4">
@@ -18530,7 +18530,7 @@
         <v>86</v>
       </c>
       <c r="V107" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.4">
@@ -18538,7 +18538,7 @@
         <v>87</v>
       </c>
       <c r="V108" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.4">
@@ -18546,7 +18546,7 @@
         <v>88</v>
       </c>
       <c r="V109" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.4">
@@ -18554,7 +18554,7 @@
         <v>89</v>
       </c>
       <c r="V110" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.4">
@@ -18562,7 +18562,7 @@
         <v>90</v>
       </c>
       <c r="V111" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.4">
@@ -18570,7 +18570,7 @@
         <v>91</v>
       </c>
       <c r="V112" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="113" spans="1:22" x14ac:dyDescent="0.4">
@@ -18578,7 +18578,7 @@
         <v>92</v>
       </c>
       <c r="V113" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="114" spans="1:22" x14ac:dyDescent="0.4">
@@ -18586,7 +18586,7 @@
         <v>93</v>
       </c>
       <c r="V114" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="115" spans="1:22" x14ac:dyDescent="0.4">
@@ -18594,7 +18594,7 @@
         <v>94</v>
       </c>
       <c r="V115" s="9" t="s">
-        <v>443</v>
+        <v>749</v>
       </c>
     </row>
     <row r="116" spans="1:22" x14ac:dyDescent="0.4">
@@ -18602,7 +18602,7 @@
         <v>95</v>
       </c>
       <c r="V116" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="117" spans="1:22" x14ac:dyDescent="0.4">
@@ -18610,7 +18610,7 @@
         <v>96</v>
       </c>
       <c r="V117" s="9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="118" spans="1:22" x14ac:dyDescent="0.4">
@@ -18618,7 +18618,7 @@
         <v>97</v>
       </c>
       <c r="V118" s="9" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="119" spans="1:22" x14ac:dyDescent="0.4">
@@ -18626,7 +18626,7 @@
         <v>98</v>
       </c>
       <c r="V119" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="120" spans="1:22" x14ac:dyDescent="0.4">
@@ -18634,7 +18634,7 @@
         <v>99</v>
       </c>
       <c r="V120" s="9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="121" spans="1:22" x14ac:dyDescent="0.4">
@@ -18642,7 +18642,7 @@
         <v>100</v>
       </c>
       <c r="V121" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="122" spans="1:22" x14ac:dyDescent="0.4">
@@ -18650,7 +18650,7 @@
         <v>101</v>
       </c>
       <c r="V122" s="9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="123" spans="1:22" x14ac:dyDescent="0.4">
@@ -18658,7 +18658,7 @@
         <v>102</v>
       </c>
       <c r="V123" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="124" spans="1:22" x14ac:dyDescent="0.4">
@@ -18666,7 +18666,7 @@
         <v>103</v>
       </c>
       <c r="V124" s="9" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="125" spans="1:22" x14ac:dyDescent="0.4">
@@ -18674,7 +18674,7 @@
         <v>104</v>
       </c>
       <c r="V125" s="9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="126" spans="1:22" x14ac:dyDescent="0.4">
@@ -18682,7 +18682,7 @@
         <v>105</v>
       </c>
       <c r="V126" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="127" spans="1:22" x14ac:dyDescent="0.4">
@@ -18690,7 +18690,7 @@
         <v>106</v>
       </c>
       <c r="V127" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="128" spans="1:22" x14ac:dyDescent="0.4">
@@ -18698,7 +18698,7 @@
         <v>107</v>
       </c>
       <c r="V128" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.4">
@@ -18706,7 +18706,7 @@
         <v>108</v>
       </c>
       <c r="V129" s="9" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.4">
@@ -18714,7 +18714,7 @@
         <v>109</v>
       </c>
       <c r="V130" s="9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.4">
@@ -18722,7 +18722,7 @@
         <v>110</v>
       </c>
       <c r="V131" s="9" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.4">
@@ -18730,7 +18730,7 @@
         <v>111</v>
       </c>
       <c r="V132" s="9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.4">
@@ -18738,83 +18738,83 @@
         <v>112</v>
       </c>
       <c r="V133" s="9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="134" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U134" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V134" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W134" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A135" s="8" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="V135" s="9" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.4">
@@ -18822,7 +18822,7 @@
         <v>113</v>
       </c>
       <c r="V136" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.4">
@@ -18830,7 +18830,7 @@
         <v>114</v>
       </c>
       <c r="V137" s="9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.4">
@@ -18838,7 +18838,7 @@
         <v>115</v>
       </c>
       <c r="V138" s="9" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.4">
@@ -18846,7 +18846,7 @@
         <v>116</v>
       </c>
       <c r="V139" s="9" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.4">
@@ -18854,7 +18854,7 @@
         <v>117</v>
       </c>
       <c r="V140" s="9" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.4">
@@ -18862,7 +18862,7 @@
         <v>118</v>
       </c>
       <c r="V141" s="9" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.4">
@@ -18870,7 +18870,7 @@
         <v>119</v>
       </c>
       <c r="V142" s="9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.4">
@@ -18878,7 +18878,7 @@
         <v>120</v>
       </c>
       <c r="V143" s="9" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.4">
@@ -18886,7 +18886,7 @@
         <v>121</v>
       </c>
       <c r="V144" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="145" spans="1:22" x14ac:dyDescent="0.4">
@@ -18894,7 +18894,7 @@
         <v>122</v>
       </c>
       <c r="V145" s="9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="146" spans="1:22" x14ac:dyDescent="0.4">
@@ -18902,7 +18902,7 @@
         <v>123</v>
       </c>
       <c r="V146" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="147" spans="1:22" x14ac:dyDescent="0.4">
@@ -18910,7 +18910,7 @@
         <v>124</v>
       </c>
       <c r="V147" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="148" spans="1:22" x14ac:dyDescent="0.4">
@@ -18918,7 +18918,7 @@
         <v>125</v>
       </c>
       <c r="V148" s="9" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="149" spans="1:22" x14ac:dyDescent="0.4">
@@ -18926,7 +18926,7 @@
         <v>126</v>
       </c>
       <c r="V149" s="9" t="s">
-        <v>475</v>
+        <v>751</v>
       </c>
     </row>
     <row r="150" spans="1:22" x14ac:dyDescent="0.4">
@@ -18934,7 +18934,7 @@
         <v>127</v>
       </c>
       <c r="V150" s="9" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="151" spans="1:22" x14ac:dyDescent="0.4">
@@ -18942,7 +18942,7 @@
         <v>128</v>
       </c>
       <c r="V151" s="9" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="152" spans="1:22" x14ac:dyDescent="0.4">
@@ -18950,7 +18950,7 @@
         <v>129</v>
       </c>
       <c r="V152" s="9" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="153" spans="1:22" x14ac:dyDescent="0.4">
@@ -18958,7 +18958,7 @@
         <v>130</v>
       </c>
       <c r="V153" s="9" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="154" spans="1:22" x14ac:dyDescent="0.4">
@@ -18966,7 +18966,7 @@
         <v>131</v>
       </c>
       <c r="V154" s="9" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="155" spans="1:22" x14ac:dyDescent="0.4">
@@ -18974,7 +18974,7 @@
         <v>132</v>
       </c>
       <c r="V155" s="9" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="156" spans="1:22" x14ac:dyDescent="0.4">
@@ -18982,7 +18982,7 @@
         <v>133</v>
       </c>
       <c r="V156" s="9" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="157" spans="1:22" x14ac:dyDescent="0.4">
@@ -18990,7 +18990,7 @@
         <v>134</v>
       </c>
       <c r="V157" s="9" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="158" spans="1:22" x14ac:dyDescent="0.4">
@@ -18998,7 +18998,7 @@
         <v>135</v>
       </c>
       <c r="V158" s="9" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="159" spans="1:22" x14ac:dyDescent="0.4">
@@ -19006,7 +19006,7 @@
         <v>136</v>
       </c>
       <c r="V159" s="9" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="160" spans="1:22" x14ac:dyDescent="0.4">
@@ -19014,7 +19014,7 @@
         <v>137</v>
       </c>
       <c r="V160" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.4">
@@ -19022,7 +19022,7 @@
         <v>138</v>
       </c>
       <c r="V161" s="9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.4">
@@ -19030,7 +19030,7 @@
         <v>139</v>
       </c>
       <c r="V162" s="9" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.4">
@@ -19038,7 +19038,7 @@
         <v>140</v>
       </c>
       <c r="V163" s="9" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.4">
@@ -19046,91 +19046,91 @@
         <v>141</v>
       </c>
       <c r="V164" s="9" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="165" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U165" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V165" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W165" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A166" s="11" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="V166" s="9" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A167" s="11" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="V167" s="9" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.4">
@@ -19138,7 +19138,7 @@
         <v>142</v>
       </c>
       <c r="V168" s="9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.4">
@@ -19146,7 +19146,7 @@
         <v>143</v>
       </c>
       <c r="V169" s="9" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.4">
@@ -19154,7 +19154,7 @@
         <v>144</v>
       </c>
       <c r="V170" s="9" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.4">
@@ -19162,7 +19162,7 @@
         <v>145</v>
       </c>
       <c r="V171" s="9" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.4">
@@ -19170,7 +19170,7 @@
         <v>146</v>
       </c>
       <c r="V172" s="9" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.4">
@@ -19178,7 +19178,7 @@
         <v>147</v>
       </c>
       <c r="V173" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.4">
@@ -19186,7 +19186,7 @@
         <v>148</v>
       </c>
       <c r="V174" s="9" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.4">
@@ -19194,7 +19194,7 @@
         <v>149</v>
       </c>
       <c r="V175" s="9" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.4">
@@ -19202,7 +19202,7 @@
         <v>150</v>
       </c>
       <c r="V176" s="9" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="177" spans="1:22" x14ac:dyDescent="0.4">
@@ -19210,7 +19210,7 @@
         <v>151</v>
       </c>
       <c r="V177" s="9" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="178" spans="1:22" x14ac:dyDescent="0.4">
@@ -19218,7 +19218,7 @@
         <v>152</v>
       </c>
       <c r="V178" s="9" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="179" spans="1:22" x14ac:dyDescent="0.4">
@@ -19226,7 +19226,7 @@
         <v>153</v>
       </c>
       <c r="V179" s="9" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="180" spans="1:22" x14ac:dyDescent="0.4">
@@ -19234,7 +19234,7 @@
         <v>154</v>
       </c>
       <c r="V180" s="9" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="181" spans="1:22" x14ac:dyDescent="0.4">
@@ -19242,7 +19242,7 @@
         <v>155</v>
       </c>
       <c r="V181" s="9" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="182" spans="1:22" x14ac:dyDescent="0.4">
@@ -19250,7 +19250,7 @@
         <v>156</v>
       </c>
       <c r="V182" s="9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="183" spans="1:22" x14ac:dyDescent="0.4">
@@ -19258,7 +19258,7 @@
         <v>157</v>
       </c>
       <c r="V183" s="9" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="184" spans="1:22" x14ac:dyDescent="0.4">
@@ -19266,7 +19266,7 @@
         <v>158</v>
       </c>
       <c r="V184" s="9" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="185" spans="1:22" x14ac:dyDescent="0.4">
@@ -19274,7 +19274,7 @@
         <v>159</v>
       </c>
       <c r="V185" s="9" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="186" spans="1:22" x14ac:dyDescent="0.4">
@@ -19282,7 +19282,7 @@
         <v>160</v>
       </c>
       <c r="V186" s="9" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="187" spans="1:22" x14ac:dyDescent="0.4">
@@ -19290,7 +19290,7 @@
         <v>161</v>
       </c>
       <c r="V187" s="9" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="188" spans="1:22" x14ac:dyDescent="0.4">
@@ -19298,7 +19298,7 @@
         <v>162</v>
       </c>
       <c r="V188" s="9" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="189" spans="1:22" x14ac:dyDescent="0.4">
@@ -19306,7 +19306,7 @@
         <v>163</v>
       </c>
       <c r="V189" s="9" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="190" spans="1:22" x14ac:dyDescent="0.4">
@@ -19314,7 +19314,7 @@
         <v>164</v>
       </c>
       <c r="V190" s="9" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="191" spans="1:22" x14ac:dyDescent="0.4">
@@ -19322,7 +19322,7 @@
         <v>165</v>
       </c>
       <c r="V191" s="9" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="192" spans="1:22" x14ac:dyDescent="0.4">
@@ -19330,7 +19330,7 @@
         <v>166</v>
       </c>
       <c r="V192" s="9" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.4">
@@ -19338,7 +19338,7 @@
         <v>167</v>
       </c>
       <c r="V193" s="9" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.4">
@@ -19346,7 +19346,7 @@
         <v>168</v>
       </c>
       <c r="V194" s="9" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.4">
@@ -19354,83 +19354,83 @@
         <v>169</v>
       </c>
       <c r="V195" s="9" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="196" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U196" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V196" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W196" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A197" s="12" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="V197" s="9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.4">
@@ -19438,7 +19438,7 @@
         <v>170</v>
       </c>
       <c r="V198" s="9" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.4">
@@ -19446,7 +19446,7 @@
         <v>171</v>
       </c>
       <c r="V199" s="9" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.4">
@@ -19454,7 +19454,7 @@
         <v>172</v>
       </c>
       <c r="V200" s="9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.4">
@@ -19462,7 +19462,7 @@
         <v>173</v>
       </c>
       <c r="V201" s="9" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.4">
@@ -19470,7 +19470,7 @@
         <v>174</v>
       </c>
       <c r="V202" s="9" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.4">
@@ -19478,7 +19478,7 @@
         <v>175</v>
       </c>
       <c r="V203" s="9" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.4">
@@ -19486,7 +19486,7 @@
         <v>176</v>
       </c>
       <c r="V204" s="9" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.4">
@@ -19494,7 +19494,7 @@
         <v>177</v>
       </c>
       <c r="V205" s="9" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.4">
@@ -19502,7 +19502,7 @@
         <v>178</v>
       </c>
       <c r="V206" s="9" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.4">
@@ -19510,7 +19510,7 @@
         <v>179</v>
       </c>
       <c r="V207" s="9" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.4">
@@ -19518,7 +19518,7 @@
         <v>180</v>
       </c>
       <c r="V208" s="9" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="209" spans="1:22" x14ac:dyDescent="0.4">
@@ -19526,7 +19526,7 @@
         <v>181</v>
       </c>
       <c r="V209" s="9" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="210" spans="1:22" x14ac:dyDescent="0.4">
@@ -19534,7 +19534,7 @@
         <v>182</v>
       </c>
       <c r="V210" s="9" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="211" spans="1:22" x14ac:dyDescent="0.4">
@@ -19542,7 +19542,7 @@
         <v>183</v>
       </c>
       <c r="V211" s="9" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="212" spans="1:22" x14ac:dyDescent="0.4">
@@ -19550,7 +19550,7 @@
         <v>184</v>
       </c>
       <c r="V212" s="9" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="213" spans="1:22" x14ac:dyDescent="0.4">
@@ -19558,7 +19558,7 @@
         <v>185</v>
       </c>
       <c r="V213" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="214" spans="1:22" x14ac:dyDescent="0.4">
@@ -19566,7 +19566,7 @@
         <v>186</v>
       </c>
       <c r="V214" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="215" spans="1:22" x14ac:dyDescent="0.4">
@@ -19574,7 +19574,7 @@
         <v>187</v>
       </c>
       <c r="V215" s="9" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="216" spans="1:22" x14ac:dyDescent="0.4">
@@ -19582,7 +19582,7 @@
         <v>188</v>
       </c>
       <c r="V216" s="9" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="217" spans="1:22" x14ac:dyDescent="0.4">
@@ -19590,7 +19590,7 @@
         <v>189</v>
       </c>
       <c r="V217" s="9" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="218" spans="1:22" x14ac:dyDescent="0.4">
@@ -19598,7 +19598,7 @@
         <v>190</v>
       </c>
       <c r="V218" s="9" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="219" spans="1:22" x14ac:dyDescent="0.4">
@@ -19606,7 +19606,7 @@
         <v>191</v>
       </c>
       <c r="V219" s="9" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="220" spans="1:22" x14ac:dyDescent="0.4">
@@ -19614,7 +19614,7 @@
         <v>192</v>
       </c>
       <c r="V220" s="9" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="221" spans="1:22" x14ac:dyDescent="0.4">
@@ -19622,7 +19622,7 @@
         <v>193</v>
       </c>
       <c r="V221" s="9" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="222" spans="1:22" x14ac:dyDescent="0.4">
@@ -19630,7 +19630,7 @@
         <v>194</v>
       </c>
       <c r="V222" s="9" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="223" spans="1:22" x14ac:dyDescent="0.4">
@@ -19638,7 +19638,7 @@
         <v>195</v>
       </c>
       <c r="V223" s="9" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="224" spans="1:22" x14ac:dyDescent="0.4">
@@ -19646,7 +19646,7 @@
         <v>196</v>
       </c>
       <c r="V224" s="9" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="225" spans="1:23" x14ac:dyDescent="0.4">
@@ -19654,7 +19654,7 @@
         <v>197</v>
       </c>
       <c r="V225" s="9" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="226" spans="1:23" x14ac:dyDescent="0.4">
@@ -19662,83 +19662,83 @@
         <v>198</v>
       </c>
       <c r="V226" s="9" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="227" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U227" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V227" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W227" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="228" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A228" s="13" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="V228" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="229" spans="1:23" x14ac:dyDescent="0.4">
@@ -19746,7 +19746,7 @@
         <v>199</v>
       </c>
       <c r="V229" s="9" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="230" spans="1:23" x14ac:dyDescent="0.4">
@@ -19754,7 +19754,7 @@
         <v>200</v>
       </c>
       <c r="V230" s="9" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="231" spans="1:23" x14ac:dyDescent="0.4">
@@ -19762,7 +19762,7 @@
         <v>201</v>
       </c>
       <c r="V231" s="9" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="232" spans="1:23" x14ac:dyDescent="0.4">
@@ -19770,7 +19770,7 @@
         <v>202</v>
       </c>
       <c r="V232" s="9" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="233" spans="1:23" x14ac:dyDescent="0.4">
@@ -19778,7 +19778,7 @@
         <v>203</v>
       </c>
       <c r="V233" s="9" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="234" spans="1:23" x14ac:dyDescent="0.4">
@@ -19786,7 +19786,7 @@
         <v>204</v>
       </c>
       <c r="V234" s="9" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="235" spans="1:23" x14ac:dyDescent="0.4">
@@ -19794,7 +19794,7 @@
         <v>205</v>
       </c>
       <c r="V235" s="9" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="236" spans="1:23" x14ac:dyDescent="0.4">
@@ -19802,7 +19802,7 @@
         <v>206</v>
       </c>
       <c r="V236" s="9" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="237" spans="1:23" x14ac:dyDescent="0.4">
@@ -19810,7 +19810,7 @@
         <v>207</v>
       </c>
       <c r="V237" s="9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="238" spans="1:23" x14ac:dyDescent="0.4">
@@ -19818,7 +19818,7 @@
         <v>208</v>
       </c>
       <c r="V238" s="9" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="239" spans="1:23" x14ac:dyDescent="0.4">
@@ -19826,7 +19826,7 @@
         <v>209</v>
       </c>
       <c r="V239" s="9" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="240" spans="1:23" x14ac:dyDescent="0.4">
@@ -19834,7 +19834,7 @@
         <v>210</v>
       </c>
       <c r="V240" s="9" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="241" spans="1:22" x14ac:dyDescent="0.4">
@@ -19842,7 +19842,7 @@
         <v>211</v>
       </c>
       <c r="V241" s="9" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="242" spans="1:22" x14ac:dyDescent="0.4">
@@ -19850,7 +19850,7 @@
         <v>212</v>
       </c>
       <c r="V242" s="9" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="243" spans="1:22" x14ac:dyDescent="0.4">
@@ -19858,7 +19858,7 @@
         <v>213</v>
       </c>
       <c r="V243" s="9" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="244" spans="1:22" x14ac:dyDescent="0.4">
@@ -19866,7 +19866,7 @@
         <v>214</v>
       </c>
       <c r="V244" s="9" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="245" spans="1:22" x14ac:dyDescent="0.4">
@@ -19874,7 +19874,7 @@
         <v>215</v>
       </c>
       <c r="V245" s="9" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="246" spans="1:22" x14ac:dyDescent="0.4">
@@ -19882,7 +19882,7 @@
         <v>216</v>
       </c>
       <c r="V246" s="9" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="247" spans="1:22" x14ac:dyDescent="0.4">
@@ -19890,7 +19890,7 @@
         <v>217</v>
       </c>
       <c r="V247" s="9" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="248" spans="1:22" x14ac:dyDescent="0.4">
@@ -19898,7 +19898,7 @@
         <v>218</v>
       </c>
       <c r="V248" s="9" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="249" spans="1:22" x14ac:dyDescent="0.4">
@@ -19906,7 +19906,7 @@
         <v>219</v>
       </c>
       <c r="V249" s="9" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="250" spans="1:22" x14ac:dyDescent="0.4">
@@ -19914,7 +19914,7 @@
         <v>220</v>
       </c>
       <c r="V250" s="9" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="251" spans="1:22" x14ac:dyDescent="0.4">
@@ -19922,7 +19922,7 @@
         <v>221</v>
       </c>
       <c r="V251" s="9" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="252" spans="1:22" x14ac:dyDescent="0.4">
@@ -19930,7 +19930,7 @@
         <v>222</v>
       </c>
       <c r="V252" s="9" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="253" spans="1:22" x14ac:dyDescent="0.4">
@@ -19938,7 +19938,7 @@
         <v>223</v>
       </c>
       <c r="V253" s="9" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="254" spans="1:22" x14ac:dyDescent="0.4">
@@ -19946,7 +19946,7 @@
         <v>224</v>
       </c>
       <c r="V254" s="9" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="255" spans="1:22" x14ac:dyDescent="0.4">
@@ -19954,7 +19954,7 @@
         <v>225</v>
       </c>
       <c r="V255" s="9" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="256" spans="1:22" x14ac:dyDescent="0.4">
@@ -19962,7 +19962,7 @@
         <v>226</v>
       </c>
       <c r="V256" s="9" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="257" spans="1:23" x14ac:dyDescent="0.4">
@@ -19970,83 +19970,83 @@
         <v>227</v>
       </c>
       <c r="V257" s="9" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="258" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U258" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V258" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W258" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="259" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A259" s="8" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="V259" s="9" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="260" spans="1:23" x14ac:dyDescent="0.4">
@@ -20054,7 +20054,7 @@
         <v>228</v>
       </c>
       <c r="V260" s="9" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="261" spans="1:23" x14ac:dyDescent="0.4">
@@ -20062,7 +20062,7 @@
         <v>229</v>
       </c>
       <c r="V261" s="9" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="262" spans="1:23" x14ac:dyDescent="0.4">
@@ -20070,7 +20070,7 @@
         <v>230</v>
       </c>
       <c r="V262" s="9" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="263" spans="1:23" x14ac:dyDescent="0.4">
@@ -20078,7 +20078,7 @@
         <v>231</v>
       </c>
       <c r="V263" s="9" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="264" spans="1:23" x14ac:dyDescent="0.4">
@@ -20086,7 +20086,7 @@
         <v>232</v>
       </c>
       <c r="V264" s="9" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="265" spans="1:23" x14ac:dyDescent="0.4">
@@ -20094,7 +20094,7 @@
         <v>233</v>
       </c>
       <c r="V265" s="9" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="266" spans="1:23" x14ac:dyDescent="0.4">
@@ -20102,7 +20102,7 @@
         <v>234</v>
       </c>
       <c r="V266" s="9" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="267" spans="1:23" x14ac:dyDescent="0.4">
@@ -20110,7 +20110,7 @@
         <v>235</v>
       </c>
       <c r="V267" s="9" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="268" spans="1:23" x14ac:dyDescent="0.4">
@@ -20118,7 +20118,7 @@
         <v>236</v>
       </c>
       <c r="V268" s="9" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="269" spans="1:23" x14ac:dyDescent="0.4">
@@ -20126,7 +20126,7 @@
         <v>237</v>
       </c>
       <c r="V269" s="9" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="270" spans="1:23" x14ac:dyDescent="0.4">
@@ -20134,7 +20134,7 @@
         <v>238</v>
       </c>
       <c r="V270" s="9" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="271" spans="1:23" x14ac:dyDescent="0.4">
@@ -20142,7 +20142,7 @@
         <v>239</v>
       </c>
       <c r="V271" s="9" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="272" spans="1:23" x14ac:dyDescent="0.4">
@@ -20150,7 +20150,7 @@
         <v>240</v>
       </c>
       <c r="V272" s="9" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="273" spans="1:22" x14ac:dyDescent="0.4">
@@ -20158,7 +20158,7 @@
         <v>241</v>
       </c>
       <c r="V273" s="9" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="274" spans="1:22" x14ac:dyDescent="0.4">
@@ -20166,7 +20166,7 @@
         <v>242</v>
       </c>
       <c r="V274" s="9" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="275" spans="1:22" x14ac:dyDescent="0.4">
@@ -20174,7 +20174,7 @@
         <v>243</v>
       </c>
       <c r="V275" s="9" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="276" spans="1:22" x14ac:dyDescent="0.4">
@@ -20182,7 +20182,7 @@
         <v>244</v>
       </c>
       <c r="V276" s="9" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="277" spans="1:22" x14ac:dyDescent="0.4">
@@ -20190,7 +20190,7 @@
         <v>245</v>
       </c>
       <c r="V277" s="9" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="278" spans="1:22" x14ac:dyDescent="0.4">
@@ -20198,7 +20198,7 @@
         <v>246</v>
       </c>
       <c r="V278" s="9" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="279" spans="1:22" x14ac:dyDescent="0.4">
@@ -20206,7 +20206,7 @@
         <v>247</v>
       </c>
       <c r="V279" s="9" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="280" spans="1:22" x14ac:dyDescent="0.4">
@@ -20214,7 +20214,7 @@
         <v>248</v>
       </c>
       <c r="V280" s="9" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="281" spans="1:22" x14ac:dyDescent="0.4">
@@ -20222,7 +20222,7 @@
         <v>249</v>
       </c>
       <c r="V281" s="9" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="282" spans="1:22" x14ac:dyDescent="0.4">
@@ -20230,7 +20230,7 @@
         <v>250</v>
       </c>
       <c r="V282" s="9" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="283" spans="1:22" x14ac:dyDescent="0.4">
@@ -20238,7 +20238,7 @@
         <v>251</v>
       </c>
       <c r="V283" s="9" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="284" spans="1:22" x14ac:dyDescent="0.4">
@@ -20246,7 +20246,7 @@
         <v>252</v>
       </c>
       <c r="V284" s="9" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="285" spans="1:22" x14ac:dyDescent="0.4">
@@ -20254,7 +20254,7 @@
         <v>253</v>
       </c>
       <c r="V285" s="9" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="286" spans="1:22" x14ac:dyDescent="0.4">
@@ -20262,7 +20262,7 @@
         <v>254</v>
       </c>
       <c r="V286" s="9" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="287" spans="1:22" x14ac:dyDescent="0.4">
@@ -20270,7 +20270,7 @@
         <v>255</v>
       </c>
       <c r="V287" s="9" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="288" spans="1:22" x14ac:dyDescent="0.4">
@@ -20278,83 +20278,83 @@
         <v>256</v>
       </c>
       <c r="V288" s="9" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="289" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U289" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V289" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W289" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="290" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A290" s="11" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="V290" s="9" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="291" spans="1:23" x14ac:dyDescent="0.4">
@@ -20362,7 +20362,7 @@
         <v>257</v>
       </c>
       <c r="V291" s="9" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="292" spans="1:23" x14ac:dyDescent="0.4">
@@ -20370,7 +20370,7 @@
         <v>258</v>
       </c>
       <c r="V292" s="9" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="293" spans="1:23" x14ac:dyDescent="0.4">
@@ -20378,7 +20378,7 @@
         <v>259</v>
       </c>
       <c r="V293" s="9" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="294" spans="1:23" x14ac:dyDescent="0.4">
@@ -20386,7 +20386,7 @@
         <v>260</v>
       </c>
       <c r="V294" s="9" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="295" spans="1:23" x14ac:dyDescent="0.4">
@@ -20394,7 +20394,7 @@
         <v>261</v>
       </c>
       <c r="V295" s="9" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="296" spans="1:23" x14ac:dyDescent="0.4">
@@ -20402,7 +20402,7 @@
         <v>262</v>
       </c>
       <c r="V296" s="9" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="297" spans="1:23" x14ac:dyDescent="0.4">
@@ -20410,7 +20410,7 @@
         <v>263</v>
       </c>
       <c r="V297" s="9" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="298" spans="1:23" x14ac:dyDescent="0.4">
@@ -20418,7 +20418,7 @@
         <v>264</v>
       </c>
       <c r="V298" s="9" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="299" spans="1:23" x14ac:dyDescent="0.4">
@@ -20426,7 +20426,7 @@
         <v>265</v>
       </c>
       <c r="V299" s="9" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="300" spans="1:23" x14ac:dyDescent="0.4">
@@ -20434,7 +20434,7 @@
         <v>266</v>
       </c>
       <c r="V300" s="9" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="301" spans="1:23" x14ac:dyDescent="0.4">
@@ -20442,7 +20442,7 @@
         <v>267</v>
       </c>
       <c r="V301" s="9" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="302" spans="1:23" x14ac:dyDescent="0.4">
@@ -20450,7 +20450,7 @@
         <v>268</v>
       </c>
       <c r="V302" s="9" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="303" spans="1:23" x14ac:dyDescent="0.4">
@@ -20458,7 +20458,7 @@
         <v>269</v>
       </c>
       <c r="V303" s="9" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="304" spans="1:23" x14ac:dyDescent="0.4">
@@ -20466,7 +20466,7 @@
         <v>270</v>
       </c>
       <c r="V304" s="9" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="305" spans="1:23" x14ac:dyDescent="0.4">
@@ -20474,7 +20474,7 @@
         <v>271</v>
       </c>
       <c r="V305" s="9" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="306" spans="1:23" x14ac:dyDescent="0.4">
@@ -20482,7 +20482,7 @@
         <v>272</v>
       </c>
       <c r="V306" s="9" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="307" spans="1:23" x14ac:dyDescent="0.4">
@@ -20490,7 +20490,7 @@
         <v>273</v>
       </c>
       <c r="V307" s="9" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="308" spans="1:23" x14ac:dyDescent="0.4">
@@ -20498,7 +20498,7 @@
         <v>274</v>
       </c>
       <c r="V308" s="9" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="309" spans="1:23" x14ac:dyDescent="0.4">
@@ -20506,7 +20506,7 @@
         <v>275</v>
       </c>
       <c r="V309" s="9" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="310" spans="1:23" x14ac:dyDescent="0.4">
@@ -20514,7 +20514,7 @@
         <v>276</v>
       </c>
       <c r="V310" s="9" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="311" spans="1:23" x14ac:dyDescent="0.4">
@@ -20522,7 +20522,7 @@
         <v>277</v>
       </c>
       <c r="V311" s="9" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="312" spans="1:23" x14ac:dyDescent="0.4">
@@ -20530,7 +20530,7 @@
         <v>278</v>
       </c>
       <c r="V312" s="9" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="313" spans="1:23" x14ac:dyDescent="0.4">
@@ -20538,7 +20538,7 @@
         <v>279</v>
       </c>
       <c r="V313" s="9" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="314" spans="1:23" x14ac:dyDescent="0.4">
@@ -20546,7 +20546,7 @@
         <v>280</v>
       </c>
       <c r="V314" s="9" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="315" spans="1:23" x14ac:dyDescent="0.4">
@@ -20554,7 +20554,7 @@
         <v>281</v>
       </c>
       <c r="V315" s="9" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="316" spans="1:23" x14ac:dyDescent="0.4">
@@ -20562,7 +20562,7 @@
         <v>282</v>
       </c>
       <c r="V316" s="9" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="317" spans="1:23" x14ac:dyDescent="0.4">
@@ -20570,7 +20570,7 @@
         <v>283</v>
       </c>
       <c r="V317" s="9" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="318" spans="1:23" x14ac:dyDescent="0.4">
@@ -20578,7 +20578,7 @@
         <v>284</v>
       </c>
       <c r="V318" s="9" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="319" spans="1:23" x14ac:dyDescent="0.4">
@@ -20586,83 +20586,83 @@
         <v>285</v>
       </c>
       <c r="V319" s="9" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="320" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U320" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V320" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W320" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="321" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A321" s="12" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="V321" s="9" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="322" spans="1:22" x14ac:dyDescent="0.4">
@@ -20670,7 +20670,7 @@
         <v>286</v>
       </c>
       <c r="V322" s="9" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="323" spans="1:22" x14ac:dyDescent="0.4">
@@ -20678,7 +20678,7 @@
         <v>287</v>
       </c>
       <c r="V323" s="9" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="324" spans="1:22" x14ac:dyDescent="0.4">
@@ -20686,7 +20686,7 @@
         <v>288</v>
       </c>
       <c r="V324" s="9" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="325" spans="1:22" x14ac:dyDescent="0.4">
@@ -20694,7 +20694,7 @@
         <v>289</v>
       </c>
       <c r="V325" s="9" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="326" spans="1:22" x14ac:dyDescent="0.4">
@@ -20702,7 +20702,7 @@
         <v>290</v>
       </c>
       <c r="V326" s="9" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="327" spans="1:22" x14ac:dyDescent="0.4">
@@ -20710,7 +20710,7 @@
         <v>291</v>
       </c>
       <c r="V327" s="9" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="328" spans="1:22" x14ac:dyDescent="0.4">
@@ -20718,7 +20718,7 @@
         <v>292</v>
       </c>
       <c r="V328" s="9" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="329" spans="1:22" x14ac:dyDescent="0.4">
@@ -20726,7 +20726,7 @@
         <v>293</v>
       </c>
       <c r="V329" s="9" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="330" spans="1:22" x14ac:dyDescent="0.4">
@@ -20734,7 +20734,7 @@
         <v>294</v>
       </c>
       <c r="V330" s="9" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="331" spans="1:22" x14ac:dyDescent="0.4">
@@ -20742,7 +20742,7 @@
         <v>295</v>
       </c>
       <c r="V331" s="9" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="332" spans="1:22" x14ac:dyDescent="0.4">
@@ -20750,7 +20750,7 @@
         <v>296</v>
       </c>
       <c r="V332" s="9" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="333" spans="1:22" x14ac:dyDescent="0.4">
@@ -20758,7 +20758,7 @@
         <v>297</v>
       </c>
       <c r="V333" s="9" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="334" spans="1:22" x14ac:dyDescent="0.4">
@@ -20766,7 +20766,7 @@
         <v>298</v>
       </c>
       <c r="V334" s="9" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="335" spans="1:22" x14ac:dyDescent="0.4">
@@ -20774,7 +20774,7 @@
         <v>299</v>
       </c>
       <c r="V335" s="9" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="336" spans="1:22" x14ac:dyDescent="0.4">
@@ -20782,7 +20782,7 @@
         <v>300</v>
       </c>
       <c r="V336" s="9" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="337" spans="1:23" x14ac:dyDescent="0.4">
@@ -20790,7 +20790,7 @@
         <v>301</v>
       </c>
       <c r="V337" s="9" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="338" spans="1:23" x14ac:dyDescent="0.4">
@@ -20798,7 +20798,7 @@
         <v>302</v>
       </c>
       <c r="V338" s="9" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="339" spans="1:23" x14ac:dyDescent="0.4">
@@ -20806,7 +20806,7 @@
         <v>303</v>
       </c>
       <c r="V339" s="9" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="340" spans="1:23" x14ac:dyDescent="0.4">
@@ -20814,7 +20814,7 @@
         <v>304</v>
       </c>
       <c r="V340" s="9" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="341" spans="1:23" x14ac:dyDescent="0.4">
@@ -20822,7 +20822,7 @@
         <v>305</v>
       </c>
       <c r="V341" s="9" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="342" spans="1:23" x14ac:dyDescent="0.4">
@@ -20830,7 +20830,7 @@
         <v>306</v>
       </c>
       <c r="V342" s="9" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="343" spans="1:23" x14ac:dyDescent="0.4">
@@ -20838,7 +20838,7 @@
         <v>307</v>
       </c>
       <c r="V343" s="9" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="344" spans="1:23" x14ac:dyDescent="0.4">
@@ -20846,7 +20846,7 @@
         <v>308</v>
       </c>
       <c r="V344" s="9" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="345" spans="1:23" x14ac:dyDescent="0.4">
@@ -20854,7 +20854,7 @@
         <v>309</v>
       </c>
       <c r="V345" s="9" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="346" spans="1:23" x14ac:dyDescent="0.4">
@@ -20862,7 +20862,7 @@
         <v>310</v>
       </c>
       <c r="V346" s="9" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="347" spans="1:23" x14ac:dyDescent="0.4">
@@ -20870,7 +20870,7 @@
         <v>311</v>
       </c>
       <c r="V347" s="9" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="348" spans="1:23" x14ac:dyDescent="0.4">
@@ -20878,7 +20878,7 @@
         <v>312</v>
       </c>
       <c r="V348" s="9" t="s">
-        <v>666</v>
+        <v>747</v>
       </c>
     </row>
     <row r="349" spans="1:23" x14ac:dyDescent="0.4">
@@ -20886,7 +20886,7 @@
         <v>313</v>
       </c>
       <c r="V349" s="9" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
     </row>
     <row r="350" spans="1:23" x14ac:dyDescent="0.4">
@@ -20894,83 +20894,83 @@
         <v>314</v>
       </c>
       <c r="V350" s="9" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="351" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="E351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="I351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="J351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="K351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="M351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="N351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="O351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="P351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="Q351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="R351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="S351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="T351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="U351" s="10" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="V351" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="W351" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="352" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A352" s="13" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="V352" s="9" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="353" spans="1:22" x14ac:dyDescent="0.4">
@@ -20978,7 +20978,7 @@
         <v>315</v>
       </c>
       <c r="V353" s="9" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="354" spans="1:22" x14ac:dyDescent="0.4">
@@ -20986,7 +20986,7 @@
         <v>316</v>
       </c>
       <c r="V354" s="9" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="355" spans="1:22" x14ac:dyDescent="0.4">
@@ -20994,7 +20994,7 @@
         <v>317</v>
       </c>
       <c r="V355" s="9" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="356" spans="1:22" x14ac:dyDescent="0.4">
@@ -21002,7 +21002,7 @@
         <v>318</v>
       </c>
       <c r="V356" s="9" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="357" spans="1:22" x14ac:dyDescent="0.4">
@@ -21010,7 +21010,7 @@
         <v>319</v>
       </c>
       <c r="V357" s="9" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="358" spans="1:22" x14ac:dyDescent="0.4">
@@ -21018,7 +21018,7 @@
         <v>320</v>
       </c>
       <c r="V358" s="9" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="359" spans="1:22" x14ac:dyDescent="0.4">
@@ -21026,7 +21026,7 @@
         <v>321</v>
       </c>
       <c r="V359" s="9" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="360" spans="1:22" x14ac:dyDescent="0.4">
@@ -21034,7 +21034,7 @@
         <v>322</v>
       </c>
       <c r="V360" s="9" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="361" spans="1:22" x14ac:dyDescent="0.4">
@@ -21042,7 +21042,7 @@
         <v>323</v>
       </c>
       <c r="V361" s="9" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="362" spans="1:22" x14ac:dyDescent="0.4">
@@ -21050,7 +21050,7 @@
         <v>324</v>
       </c>
       <c r="V362" s="9" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="363" spans="1:22" x14ac:dyDescent="0.4">
@@ -21058,7 +21058,7 @@
         <v>325</v>
       </c>
       <c r="V363" s="9" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="364" spans="1:22" x14ac:dyDescent="0.4">
@@ -21066,7 +21066,7 @@
         <v>326</v>
       </c>
       <c r="V364" s="9" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="365" spans="1:22" x14ac:dyDescent="0.4">
@@ -21074,7 +21074,7 @@
         <v>327</v>
       </c>
       <c r="V365" s="9" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="366" spans="1:22" x14ac:dyDescent="0.4">
@@ -21082,7 +21082,7 @@
         <v>328</v>
       </c>
       <c r="V366" s="9" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="367" spans="1:22" x14ac:dyDescent="0.4">
@@ -21090,7 +21090,7 @@
         <v>329</v>
       </c>
       <c r="V367" s="9" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="368" spans="1:22" x14ac:dyDescent="0.4">
@@ -21098,7 +21098,7 @@
         <v>330</v>
       </c>
       <c r="V368" s="9" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="369" spans="1:23" x14ac:dyDescent="0.4">
@@ -21106,7 +21106,7 @@
         <v>331</v>
       </c>
       <c r="V369" s="9" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="370" spans="1:23" x14ac:dyDescent="0.4">
@@ -21114,7 +21114,7 @@
         <v>332</v>
       </c>
       <c r="V370" s="9" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
     </row>
     <row r="371" spans="1:23" x14ac:dyDescent="0.4">
@@ -21122,7 +21122,7 @@
         <v>333</v>
       </c>
       <c r="V371" s="9" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
     </row>
     <row r="372" spans="1:23" x14ac:dyDescent="0.4">
@@ -21130,7 +21130,7 @@
         <v>334</v>
       </c>
       <c r="V372" s="9" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="373" spans="1:23" x14ac:dyDescent="0.4">
@@ -21138,7 +21138,7 @@
         <v>335</v>
       </c>
       <c r="V373" s="9" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
     </row>
     <row r="374" spans="1:23" x14ac:dyDescent="0.4">
@@ -21146,7 +21146,7 @@
         <v>336</v>
       </c>
       <c r="V374" s="9" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="375" spans="1:23" x14ac:dyDescent="0.4">
@@ -21154,7 +21154,7 @@
         <v>337</v>
       </c>
       <c r="V375" s="9" t="s">
-        <v>692</v>
+        <v>750</v>
       </c>
     </row>
     <row r="376" spans="1:23" x14ac:dyDescent="0.4">
@@ -21162,7 +21162,7 @@
         <v>338</v>
       </c>
       <c r="V376" s="9" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="377" spans="1:23" x14ac:dyDescent="0.4">
@@ -21170,7 +21170,7 @@
         <v>339</v>
       </c>
       <c r="V377" s="9" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
     </row>
     <row r="378" spans="1:23" x14ac:dyDescent="0.4">
@@ -21178,7 +21178,7 @@
         <v>340</v>
       </c>
       <c r="V378" s="9" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="379" spans="1:23" x14ac:dyDescent="0.4">
@@ -21186,7 +21186,7 @@
         <v>341</v>
       </c>
       <c r="V379" s="9" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="380" spans="1:23" x14ac:dyDescent="0.4">
@@ -21194,7 +21194,7 @@
         <v>342</v>
       </c>
       <c r="V380" s="9" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
     </row>
     <row r="381" spans="1:23" x14ac:dyDescent="0.4">
@@ -21202,78 +21202,78 @@
         <v>343</v>
       </c>
       <c r="V381" s="9" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="382" spans="1:23" s="10" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A382" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B382" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="C382" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="D382" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="E382" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="F382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="G382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="H382" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="I382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="J382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="K382" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="L382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="M382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="N382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="O382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="P382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="Q382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="R382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="S382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="T382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="U382" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="V382" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="B382" s="10" t="s">
-        <v>741</v>
-      </c>
-      <c r="C382" s="10" t="s">
-        <v>742</v>
-      </c>
-      <c r="D382" s="10" t="s">
-        <v>742</v>
-      </c>
-      <c r="E382" s="10" t="s">
-        <v>742</v>
-      </c>
-      <c r="F382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="G382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="H382" s="10" t="s">
-        <v>742</v>
-      </c>
-      <c r="I382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="J382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="K382" s="10" t="s">
-        <v>742</v>
-      </c>
-      <c r="L382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="M382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="N382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="O382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="P382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="Q382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="R382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="S382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="T382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="U382" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="V382" s="10" t="s">
-        <v>746</v>
-      </c>
       <c r="W382" s="10" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
   </sheetData>
